--- a/files/2026-09-03/RTL_vs_competitors_price_diff_2026-09-03.xlsx
+++ b/files/2026-09-03/RTL_vs_competitors_price_diff_2026-09-03.xlsx
@@ -172,6 +172,750 @@
     <t xml:space="preserve">Froza</t>
   </si>
   <si>
+    <t xml:space="preserve">08886-02805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Япония), (4л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5325.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5896.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4749.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-576.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4928.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-397.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5795.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5724.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.15999999999985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 576 руб. (10.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08886-81875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota CVTF Fluid FE, для вариаторов, (Таиланд), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4836.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5514.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4561.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-275.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1692 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4510.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-326.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6090.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1254.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">254 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4939.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.18000000000029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 326 руб. (6.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 4 510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08886-81885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Таиланд), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4419.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5038.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3971.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-448.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4076.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-342.80999999999995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">906.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4776.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.97000000000025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 448 руб. (10.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Febi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6248.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5763.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-485.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5977.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-270.5100000000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6163.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 5 763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4024610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3625.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4133.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3360.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-265.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2031 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3476.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-149.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3940.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4047.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422.4000000000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 265 руб. (7.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550061548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes-Benz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3499.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3531.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2973.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-526.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 526 руб. (15.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83215A1C740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло BMW Twin Power Turbo SN 0W-30 Longlife-12 FE (C2), (Германия/Испания), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2044.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2262.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1914.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-130.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 130 руб. (6.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 1 914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989320911ABDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1685.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1921.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1065.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-620.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1161.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-523.4000000000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 620 руб. (36.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-36.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989440411FULW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1792.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2043.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1436.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-356.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-296.5899999999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2035.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 356 руб. (19.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989671011FBDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1241.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1415.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1033.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-208.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1208 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1077.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-163.32999999999993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 208 руб. (16.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681011FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">976.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1113.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-65.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7718 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-37.700000000000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1165.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 65 руб. (6.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681013FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5095.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5809.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-534.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-585.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 585 руб. (11.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691011FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1259.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1028.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-231.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1403 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1067.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-192.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 231 руб. (18.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-18.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691013FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5486.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6255.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-650.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1791 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5016.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-470.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 650 руб. (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM10038-4EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3336.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3804.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2775.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-561.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2860.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-476.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 561 руб. (16.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2809.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3203.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2337.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-472.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2845.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.289999999999964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 472 руб. (16.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3916.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4336.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3197.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-719.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3323.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-593.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 719 руб. (18.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-18.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT5QMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">791.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-63.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2710 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">751.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-39.700000000000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">890.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.20000000000005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 63 руб. (8.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">08880-83717</t>
   </si>
   <si>
@@ -211,7 +955,7 @@
     <t xml:space="preserve">518.71</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 34 руб. (1.3%)</t>
+    <t xml:space="preserve">конкурент ниже на 34 руб. (1.3%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 2 561</t>
@@ -220,321 +964,6 @@
     <t xml:space="preserve">-1.3</t>
   </si>
   <si>
-    <t xml:space="preserve">08886-02805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Япония), (4л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5325.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5896.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4749.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-576.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4928.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-397.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5795.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5724.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.15999999999985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 576 руб. (10.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08886-81875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota CVTF Fluid FE, для вариаторов, (Таиланд), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4836.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5514.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4561.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-275.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1692 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4510.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-326.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6090.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1254.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">254 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4939.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.18000000000029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 326 руб. (6.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 4 510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08886-81885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Таиланд), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4419.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5038.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3971.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-448.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4076.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-342.80999999999995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">906.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4776.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.97000000000025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 448 руб. (10.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Febi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6248.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5763.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-485.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5977.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-270.5100000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6163.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 5 763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4024610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsubishi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3625.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4133.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3360.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-265.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2031 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3476.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-149.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3940.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4047.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">422.4000000000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 265 руб. (7.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550061548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercedes-Benz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3499.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3531.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2973.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-526.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 526 руб. (15.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-15.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83215A1C740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло BMW Twin Power Turbo SN 0W-30 Longlife-12 FE (C2), (Германия/Испания), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2044.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2262.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1914.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-130.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 130 руб. (6.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 1 914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.4</t>
-  </si>
-  <si>
     <t xml:space="preserve">83215B5BFA4</t>
   </si>
   <si>
@@ -562,7 +991,7 @@
     <t xml:space="preserve">145.96000000000004</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 32 руб. (2.3%)</t>
+    <t xml:space="preserve">конкурент ниже на 32 руб. (2.3%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 386</t>
@@ -571,42 +1000,6 @@
     <t xml:space="preserve">-2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989320911ABDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1685.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1921.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1065.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-620.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1161.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-523.4000000000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 620 руб. (36.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-36.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">A000989440411FDNE</t>
   </si>
   <si>
@@ -628,7 +1021,7 @@
     <t xml:space="preserve">-82.3599999999999</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 82 руб. (4.9%)</t>
+    <t xml:space="preserve">конкурент ниже на 82 руб. (4.9%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 606.64</t>
@@ -640,237 +1033,6 @@
     <t xml:space="preserve">-4.9</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989440411FULW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1792.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2043.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1436.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-356.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">911 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-296.5899999999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2035.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 356 руб. (19.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-19.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989671011FBDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1241.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1415.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1033.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-208.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1208 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1077.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-163.32999999999993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 208 руб. (16.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681011FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">976.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1113.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">911.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-65.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7718 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">938.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-37.700000000000045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1165.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 65 руб. (6.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681013FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5095.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5809.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-534.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-585.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 585 руб. (11.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691011FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1259.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1028.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-231.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1403 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1067.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-192.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 231 руб. (18.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-18.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691013FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5486.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6255.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-650.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1791 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5016.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-470.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 650 руб. (11.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">KE90799932</t>
   </si>
   <si>
@@ -907,175 +1069,13 @@
     <t xml:space="preserve">535.9000000000001</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 16 руб. (0.9%)</t>
+    <t xml:space="preserve">конкурент ниже на 16 руб. (0.9%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 1 782</t>
   </si>
   <si>
     <t xml:space="preserve">-0.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM10038-4EN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3336.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3804.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2775.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-561.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2860.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-476.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 561 руб. (16.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2809.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3203.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2337.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-472.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2845.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.289999999999964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 472 руб. (16.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3916.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4336.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3197.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-719.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3323.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-593.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 719 руб. (18.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-18.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XT5QMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">791.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">902.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">728.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-63.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2710 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">751.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-39.700000000000045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">890.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.20000000000005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 63 руб. (8.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.0</t>
   </si>
   <si>
     <t xml:space="preserve">08234P99F4PY1</t>
@@ -1714,7 +1714,7 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -1723,49 +1723,49 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
         <v>57</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>58</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" t="s">
         <v>59</v>
       </c>
-      <c r="I3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>60</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
         <v>61</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>62</v>
-      </c>
-      <c r="M3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" t="s">
-        <v>64</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="S3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1780,16 +1780,16 @@
         <v>48</v>
       </c>
       <c r="Y3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AC3" t="s">
         <v>53</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
@@ -1812,49 +1812,49 @@
         <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" t="s">
         <v>74</v>
       </c>
-      <c r="I4" t="s">
-        <v>73</v>
-      </c>
       <c r="J4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L4" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
       </c>
       <c r="P4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="T4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1869,16 +1869,16 @@
         <v>48</v>
       </c>
       <c r="Y4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Z4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AA4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AC4" t="s">
         <v>53</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
@@ -1901,43 +1901,43 @@
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O5" t="s">
         <v>42</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="Q5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R5" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="S5" t="s">
         <v>100</v>
@@ -1964,7 +1964,7 @@
         <v>103</v>
       </c>
       <c r="AA5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="s">
         <v>104</v>
@@ -1981,7 +1981,7 @@
         <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1990,16 +1990,16 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H6" t="s">
         <v>109</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s">
         <v>110</v>
@@ -2008,31 +2008,31 @@
         <v>111</v>
       </c>
       <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
         <v>112</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>113</v>
-      </c>
-      <c r="N6" t="s">
-        <v>114</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="Q6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" t="s">
+        <v>114</v>
+      </c>
+      <c r="T6" t="s">
         <v>115</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" t="s">
-        <v>116</v>
-      </c>
-      <c r="T6" t="s">
-        <v>117</v>
       </c>
       <c r="U6" t="s">
         <v>42</v>
@@ -2047,16 +2047,16 @@
         <v>48</v>
       </c>
       <c r="Y6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s">
         <v>111</v>
       </c>
       <c r="AB6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AC6" t="s">
         <v>53</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
         <v>121</v>
-      </c>
-      <c r="B7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" t="s">
-        <v>123</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -2079,25 +2079,25 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" t="s">
         <v>124</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" t="s">
         <v>125</v>
       </c>
-      <c r="H7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>126</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>127</v>
-      </c>
-      <c r="L7" t="s">
-        <v>48</v>
       </c>
       <c r="M7" t="s">
         <v>128</v>
@@ -2109,19 +2109,19 @@
         <v>42</v>
       </c>
       <c r="P7" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="Q7" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="S7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="T7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="U7" t="s">
         <v>42</v>
@@ -2136,16 +2136,16 @@
         <v>48</v>
       </c>
       <c r="Y7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Z7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AA7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AB7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AC7" t="s">
         <v>53</v>
@@ -2153,13 +2153,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -2168,87 +2168,87 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L8" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="M8" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="N8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" t="s">
+        <v>48</v>
+      </c>
+      <c r="P8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" t="s">
+        <v>48</v>
+      </c>
+      <c r="U8" t="s">
+        <v>48</v>
+      </c>
+      <c r="V8" t="s">
+        <v>48</v>
+      </c>
+      <c r="W8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA8" t="s">
         <v>145</v>
       </c>
-      <c r="O8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P8" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>147</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="AB8" t="s">
         <v>148</v>
       </c>
-      <c r="S8" t="s">
-        <v>149</v>
-      </c>
-      <c r="T8" t="s">
-        <v>150</v>
-      </c>
-      <c r="U8" t="s">
-        <v>42</v>
-      </c>
-      <c r="V8" t="s">
-        <v>48</v>
-      </c>
-      <c r="W8" t="s">
-        <v>48</v>
-      </c>
-      <c r="X8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>153</v>
-      </c>
       <c r="AC8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2257,73 +2257,73 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" t="s">
+        <v>154</v>
+      </c>
+      <c r="N9" t="s">
+        <v>155</v>
+      </c>
+      <c r="O9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R9" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" t="s">
+        <v>48</v>
+      </c>
+      <c r="T9" t="s">
+        <v>48</v>
+      </c>
+      <c r="U9" t="s">
+        <v>48</v>
+      </c>
+      <c r="V9" t="s">
+        <v>48</v>
+      </c>
+      <c r="W9" t="s">
+        <v>48</v>
+      </c>
+      <c r="X9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z9" t="s">
         <v>157</v>
       </c>
-      <c r="G9" t="s">
+      <c r="AA9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB9" t="s">
         <v>158</v>
-      </c>
-      <c r="H9" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" t="s">
-        <v>158</v>
-      </c>
-      <c r="J9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K9" t="s">
-        <v>161</v>
-      </c>
-      <c r="L9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" t="s">
-        <v>48</v>
-      </c>
-      <c r="U9" t="s">
-        <v>48</v>
-      </c>
-      <c r="V9" t="s">
-        <v>48</v>
-      </c>
-      <c r="W9" t="s">
-        <v>48</v>
-      </c>
-      <c r="X9" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>164</v>
       </c>
       <c r="AC9" t="s">
         <v>48</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -2346,31 +2346,31 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="L10" t="s">
         <v>48</v>
       </c>
       <c r="M10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
@@ -2403,16 +2403,16 @@
         <v>48</v>
       </c>
       <c r="Y10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Z10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AA10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AB10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AC10" t="s">
         <v>48</v>
@@ -2420,13 +2420,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2435,52 +2435,52 @@
         <v>33</v>
       </c>
       <c r="F11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I11" t="s">
+        <v>174</v>
+      </c>
+      <c r="J11" t="s">
+        <v>176</v>
+      </c>
+      <c r="K11" t="s">
         <v>177</v>
       </c>
-      <c r="G11" t="s">
+      <c r="L11" t="s">
         <v>178</v>
       </c>
-      <c r="H11" t="s">
+      <c r="M11" t="s">
         <v>179</v>
       </c>
-      <c r="I11" t="s">
-        <v>178</v>
-      </c>
-      <c r="J11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>180</v>
-      </c>
-      <c r="N11" t="s">
-        <v>181</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
       </c>
       <c r="P11" t="s">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="Q11" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="R11" t="s">
-        <v>48</v>
+        <v>183</v>
       </c>
       <c r="S11" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="T11" t="s">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="U11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="V11" t="s">
         <v>48</v>
@@ -2498,13 +2498,13 @@
         <v>185</v>
       </c>
       <c r="AA11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AB11" t="s">
         <v>186</v>
       </c>
       <c r="AC11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -2515,7 +2515,7 @@
         <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -2542,13 +2542,13 @@
         <v>193</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>194</v>
       </c>
       <c r="M12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O12" t="s">
         <v>42</v>
@@ -2581,16 +2581,16 @@
         <v>48</v>
       </c>
       <c r="Y12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA12" t="s">
         <v>193</v>
       </c>
       <c r="AB12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC12" t="s">
         <v>48</v>
@@ -2598,13 +2598,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -2613,43 +2613,43 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I13" t="s">
         <v>203</v>
       </c>
-      <c r="I13" t="s">
-        <v>202</v>
-      </c>
       <c r="J13" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="L13" t="s">
-        <v>48</v>
+        <v>207</v>
       </c>
       <c r="M13" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N13" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O13" t="s">
         <v>42</v>
       </c>
       <c r="P13" t="s">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="Q13" t="s">
-        <v>48</v>
+        <v>211</v>
       </c>
       <c r="R13" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="S13" t="s">
         <v>48</v>
@@ -2670,16 +2670,16 @@
         <v>48</v>
       </c>
       <c r="Y13" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA13" t="s">
         <v>206</v>
       </c>
-      <c r="Z13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>208</v>
-      </c>
       <c r="AB13" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="AC13" t="s">
         <v>48</v>
@@ -2687,13 +2687,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -2702,73 +2702,73 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H14" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I14" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J14" t="s">
-        <v>215</v>
+        <v>76</v>
       </c>
       <c r="K14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L14" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M14" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O14" t="s">
         <v>42</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>48</v>
       </c>
       <c r="Q14" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" t="s">
+        <v>48</v>
+      </c>
+      <c r="S14" t="s">
+        <v>48</v>
+      </c>
+      <c r="T14" t="s">
+        <v>48</v>
+      </c>
+      <c r="U14" t="s">
+        <v>48</v>
+      </c>
+      <c r="V14" t="s">
+        <v>48</v>
+      </c>
+      <c r="W14" t="s">
+        <v>48</v>
+      </c>
+      <c r="X14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA14" t="s">
         <v>221</v>
       </c>
-      <c r="R14" t="s">
-        <v>222</v>
-      </c>
-      <c r="S14" t="s">
-        <v>48</v>
-      </c>
-      <c r="T14" t="s">
-        <v>48</v>
-      </c>
-      <c r="U14" t="s">
-        <v>48</v>
-      </c>
-      <c r="V14" t="s">
-        <v>48</v>
-      </c>
-      <c r="W14" t="s">
-        <v>48</v>
-      </c>
-      <c r="X14" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y14" t="s">
+      <c r="AB14" t="s">
         <v>223</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>224</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>225</v>
       </c>
       <c r="AC14" t="s">
         <v>48</v>
@@ -2776,13 +2776,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -2791,31 +2791,31 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I15" t="s">
+        <v>227</v>
+      </c>
+      <c r="J15" t="s">
         <v>228</v>
       </c>
-      <c r="G15" t="s">
+      <c r="K15" t="s">
         <v>229</v>
       </c>
-      <c r="H15" t="s">
+      <c r="L15" t="s">
         <v>230</v>
       </c>
-      <c r="I15" t="s">
-        <v>229</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>231</v>
       </c>
-      <c r="K15" t="s">
+      <c r="N15" t="s">
         <v>232</v>
-      </c>
-      <c r="L15" t="s">
-        <v>233</v>
-      </c>
-      <c r="M15" t="s">
-        <v>234</v>
-      </c>
-      <c r="N15" t="s">
-        <v>235</v>
       </c>
       <c r="O15" t="s">
         <v>42</v>
@@ -2848,16 +2848,16 @@
         <v>48</v>
       </c>
       <c r="Y15" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Z15" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AA15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AB15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AC15" t="s">
         <v>48</v>
@@ -2865,13 +2865,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -2880,43 +2880,43 @@
         <v>33</v>
       </c>
       <c r="F16" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" t="s">
+        <v>239</v>
+      </c>
+      <c r="H16" t="s">
+        <v>240</v>
+      </c>
+      <c r="I16" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s">
         <v>241</v>
       </c>
-      <c r="G16" t="s">
+      <c r="L16" t="s">
         <v>242</v>
       </c>
-      <c r="H16" t="s">
+      <c r="M16" t="s">
         <v>243</v>
       </c>
-      <c r="I16" t="s">
-        <v>242</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="N16" t="s">
         <v>244</v>
-      </c>
-      <c r="K16" t="s">
-        <v>245</v>
-      </c>
-      <c r="L16" t="s">
-        <v>246</v>
-      </c>
-      <c r="M16" t="s">
-        <v>247</v>
-      </c>
-      <c r="N16" t="s">
-        <v>248</v>
       </c>
       <c r="O16" t="s">
         <v>42</v>
       </c>
       <c r="P16" t="s">
-        <v>249</v>
+        <v>48</v>
       </c>
       <c r="Q16" t="s">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="R16" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="S16" t="s">
         <v>48</v>
@@ -2937,16 +2937,16 @@
         <v>48</v>
       </c>
       <c r="Y16" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Z16" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AA16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AB16" t="s">
-        <v>104</v>
+        <v>247</v>
       </c>
       <c r="AC16" t="s">
         <v>48</v>
@@ -2954,13 +2954,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -2969,31 +2969,31 @@
         <v>33</v>
       </c>
       <c r="F17" t="s">
+        <v>251</v>
+      </c>
+      <c r="G17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" t="s">
+        <v>253</v>
+      </c>
+      <c r="I17" t="s">
+        <v>252</v>
+      </c>
+      <c r="J17" t="s">
+        <v>254</v>
+      </c>
+      <c r="K17" t="s">
         <v>255</v>
       </c>
-      <c r="G17" t="s">
+      <c r="L17" t="s">
         <v>256</v>
       </c>
-      <c r="H17" t="s">
+      <c r="M17" t="s">
         <v>257</v>
       </c>
-      <c r="I17" t="s">
-        <v>256</v>
-      </c>
-      <c r="J17" t="s">
-        <v>92</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="N17" t="s">
         <v>258</v>
-      </c>
-      <c r="L17" t="s">
-        <v>259</v>
-      </c>
-      <c r="M17" t="s">
-        <v>95</v>
-      </c>
-      <c r="N17" t="s">
-        <v>260</v>
       </c>
       <c r="O17" t="s">
         <v>42</v>
@@ -3026,16 +3026,16 @@
         <v>48</v>
       </c>
       <c r="Y17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Z17" t="s">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="AA17" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AB17" t="s">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="AC17" t="s">
         <v>48</v>
@@ -3043,13 +3043,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -3058,87 +3058,87 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
+        <v>263</v>
+      </c>
+      <c r="G18" t="s">
+        <v>264</v>
+      </c>
+      <c r="H18" t="s">
         <v>265</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
+        <v>264</v>
+      </c>
+      <c r="J18" t="s">
         <v>266</v>
       </c>
-      <c r="H18" t="s">
-        <v>215</v>
-      </c>
-      <c r="I18" t="s">
-        <v>266</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>267</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>268</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
+        <v>48</v>
+      </c>
+      <c r="N18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>48</v>
+      </c>
+      <c r="R18" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18" t="s">
         <v>269</v>
       </c>
-      <c r="M18" t="s">
+      <c r="T18" t="s">
         <v>270</v>
       </c>
-      <c r="N18" t="s">
+      <c r="U18" t="s">
+        <v>42</v>
+      </c>
+      <c r="V18" t="s">
+        <v>48</v>
+      </c>
+      <c r="W18" t="s">
+        <v>48</v>
+      </c>
+      <c r="X18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y18" t="s">
         <v>271</v>
       </c>
-      <c r="O18" t="s">
-        <v>42</v>
-      </c>
-      <c r="P18" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>48</v>
-      </c>
-      <c r="R18" t="s">
-        <v>48</v>
-      </c>
-      <c r="S18" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" t="s">
-        <v>48</v>
-      </c>
-      <c r="U18" t="s">
-        <v>48</v>
-      </c>
-      <c r="V18" t="s">
-        <v>48</v>
-      </c>
-      <c r="W18" t="s">
-        <v>48</v>
-      </c>
-      <c r="X18" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y18" t="s">
+      <c r="Z18" t="s">
         <v>272</v>
       </c>
-      <c r="Z18" t="s">
-        <v>273</v>
-      </c>
       <c r="AA18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AB18" t="s">
-        <v>274</v>
+        <v>199</v>
       </c>
       <c r="AC18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -3147,31 +3147,31 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G19" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" t="s">
         <v>277</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
+        <v>276</v>
+      </c>
+      <c r="J19" t="s">
         <v>278</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" t="s">
         <v>279</v>
       </c>
-      <c r="I19" t="s">
-        <v>278</v>
-      </c>
-      <c r="J19" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>280</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>281</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>282</v>
-      </c>
-      <c r="N19" t="s">
-        <v>283</v>
       </c>
       <c r="O19" t="s">
         <v>42</v>
@@ -3204,16 +3204,16 @@
         <v>48</v>
       </c>
       <c r="Y19" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z19" t="s">
         <v>284</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB19" t="s">
         <v>285</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>286</v>
       </c>
       <c r="AC19" t="s">
         <v>48</v>
@@ -3221,13 +3221,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" t="s">
         <v>287</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>288</v>
-      </c>
-      <c r="C20" t="s">
-        <v>289</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -3236,25 +3236,25 @@
         <v>33</v>
       </c>
       <c r="F20" t="s">
+        <v>289</v>
+      </c>
+      <c r="G20" t="s">
         <v>290</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>291</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
+        <v>290</v>
+      </c>
+      <c r="J20" t="s">
         <v>292</v>
       </c>
-      <c r="I20" t="s">
-        <v>291</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>293</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>294</v>
-      </c>
-      <c r="L20" t="s">
-        <v>48</v>
       </c>
       <c r="M20" t="s">
         <v>295</v>
@@ -3299,7 +3299,7 @@
         <v>300</v>
       </c>
       <c r="AA20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB20" t="s">
         <v>301</v>
@@ -3364,13 +3364,13 @@
         <v>48</v>
       </c>
       <c r="S21" t="s">
-        <v>48</v>
+        <v>313</v>
       </c>
       <c r="T21" t="s">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="U21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="V21" t="s">
         <v>48</v>
@@ -3382,30 +3382,30 @@
         <v>48</v>
       </c>
       <c r="Y21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z21" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA21" t="s">
         <v>309</v>
       </c>
       <c r="AB21" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="AC21" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B22" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -3414,34 +3414,34 @@
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G22" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H22" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="I22" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J22" t="s">
-        <v>320</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s">
-        <v>321</v>
+        <v>48</v>
       </c>
       <c r="L22" t="s">
-        <v>322</v>
+        <v>48</v>
       </c>
       <c r="M22" t="s">
-        <v>48</v>
+        <v>323</v>
       </c>
       <c r="N22" t="s">
-        <v>48</v>
+        <v>324</v>
       </c>
       <c r="O22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P22" t="s">
         <v>48</v>
@@ -3453,10 +3453,10 @@
         <v>48</v>
       </c>
       <c r="S22" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="T22" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="U22" t="s">
         <v>42</v>
@@ -3471,16 +3471,16 @@
         <v>48</v>
       </c>
       <c r="Y22" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z22" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA22" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AB22" t="s">
-        <v>238</v>
+        <v>329</v>
       </c>
       <c r="AC22" t="s">
         <v>53</v>
@@ -3488,13 +3488,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -3503,25 +3503,25 @@
         <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G23" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H23" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I23" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J23" t="s">
-        <v>332</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s">
-        <v>333</v>
+        <v>48</v>
       </c>
       <c r="L23" t="s">
-        <v>334</v>
+        <v>48</v>
       </c>
       <c r="M23" t="s">
         <v>335</v>
@@ -3566,10 +3566,10 @@
         <v>338</v>
       </c>
       <c r="AA23" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AB23" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AC23" t="s">
         <v>48</v>
@@ -3577,13 +3577,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -3592,25 +3592,25 @@
         <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G24" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H24" t="s">
+        <v>346</v>
+      </c>
+      <c r="I24" t="s">
         <v>345</v>
       </c>
-      <c r="I24" t="s">
-        <v>344</v>
-      </c>
       <c r="J24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L24" t="s">
-        <v>348</v>
+        <v>48</v>
       </c>
       <c r="M24" t="s">
         <v>349</v>
@@ -3655,7 +3655,7 @@
         <v>354</v>
       </c>
       <c r="AA24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AB24" t="s">
         <v>355</v>
@@ -3850,7 +3850,7 @@
         <v>387</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>304</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -3862,13 +3862,13 @@
         <v>388</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
       <c r="H27" t="s">
-        <v>59</v>
+        <v>307</v>
       </c>
       <c r="I27" t="s">
-        <v>58</v>
+        <v>306</v>
       </c>
       <c r="J27" t="s">
         <v>389</v>
@@ -3939,7 +3939,7 @@
         <v>397</v>
       </c>
       <c r="C28" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -4028,7 +4028,7 @@
         <v>410</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -4117,7 +4117,7 @@
         <v>428</v>
       </c>
       <c r="C30" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -4384,7 +4384,7 @@
         <v>456</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -4473,7 +4473,7 @@
         <v>461</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -4562,7 +4562,7 @@
         <v>465</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
@@ -4829,7 +4829,7 @@
         <v>484</v>
       </c>
       <c r="C38" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="D38" t="s">
         <v>32</v>
